--- a/IntegrationAPITool/artifacts/requirement_doc/InterestPayment.xlsx
+++ b/IntegrationAPITool/artifacts/requirement_doc/InterestPayment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://finastra.sharepoint.com/teams/SOAPtoRESTAPI/Shared Documents/General/3. Loan Interest Payment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asrivas3\git\remote_agent\IntegrationAPITool\artifacts\requirement_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{425E5F86-61E5-423A-A7CC-C9791D00A1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F0DF37-5AC3-4F85-AD54-4205BA4FAE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="736" firstSheet="1" activeTab="1" xr2:uid="{8CA9F380-F4A4-46F0-8E8E-A76D9066CD93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="736" firstSheet="1" activeTab="8" xr2:uid="{8CA9F380-F4A4-46F0-8E8E-A76D9066CD93}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="37" r:id="rId1"/>
@@ -29,13 +29,13 @@
     <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Create!$A$5:$P$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Create!$A$6:$P$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Loan Change Transaction'!$A$8:$N$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Update!$A$5:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Update!$A$6:$P$29</definedName>
     <definedName name="_Hlk86385617" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="_Hlk86385617" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
-    <definedName name="_Toc139059209" localSheetId="2">Create!$B$23</definedName>
-    <definedName name="_Toc139059209" localSheetId="4">Update!$B$24</definedName>
+    <definedName name="_Toc139059209" localSheetId="2">Create!$B$24</definedName>
+    <definedName name="_Toc139059209" localSheetId="4">Update!$B$25</definedName>
     <definedName name="_Toc81484211" localSheetId="9">OutOfScope!$A$15</definedName>
     <definedName name="_Toc81484212" localSheetId="9">OutOfScope!$A$16</definedName>
     <definedName name="_Toc81484213" localSheetId="9">OutOfScope!$A$17</definedName>
@@ -57,9 +57,9 @@
     <definedName name="feePaidByProfileType3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
     <definedName name="feePaidByServicingGroupAlias3256" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="feePaidByServicingGroupAlias3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
-    <definedName name="GA7610_2" localSheetId="2">Create!$F$18</definedName>
+    <definedName name="GA7610_2" localSheetId="2">Create!$F$19</definedName>
     <definedName name="GA7610_2" localSheetId="4">Update!#REF!</definedName>
-    <definedName name="GA7610_3" localSheetId="2">Create!$F$19</definedName>
+    <definedName name="GA7610_3" localSheetId="2">Create!$F$20</definedName>
     <definedName name="GA7610_3" localSheetId="4">Update!#REF!</definedName>
     <definedName name="nonCashPrincipalPaydown1" localSheetId="2">Create!#REF!</definedName>
     <definedName name="nonCashPrincipalPaydown1" localSheetId="4">Update!#REF!</definedName>
@@ -67,7 +67,7 @@
     <definedName name="originalExpiryDate3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
     <definedName name="ProfTypeUpd3465" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="ProfTypeUpd3465" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
-    <definedName name="transactionDate1" localSheetId="2">Create!$F$11</definedName>
+    <definedName name="transactionDate1" localSheetId="2">Create!$F$12</definedName>
     <definedName name="transactionDate1" localSheetId="4">Update!#REF!</definedName>
     <definedName name="useDistributionList3256" localSheetId="6">Delete!#REF!</definedName>
     <definedName name="useDistributionList3256" localSheetId="10">'Loan Change Transaction'!#REF!</definedName>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="788">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -2925,6 +2925,12 @@
   </si>
   <si>
     <t>ISDRD</t>
+  </si>
+  <si>
+    <t>ENTITY_NAME</t>
+  </si>
+  <si>
+    <t>LoanInterestPayment</t>
   </si>
 </sst>
 </file>
@@ -3314,7 +3320,7 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3460,6 +3466,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3493,7 +3502,7 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3820,9 +3829,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3860,7 +3869,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3966,7 +3975,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4108,7 +4117,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4117,17 +4126,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB31404B-DF48-4962-9CC3-4DEB2DFA7F7B}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
-    <col min="4" max="4" width="107.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="4" max="4" width="107.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -4150,7 +4159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -4163,7 +4172,7 @@
       <c r="D2" s="16"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:7" s="24" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f>A2+1</f>
         <v>2</v>
@@ -4177,7 +4186,7 @@
       <c r="D3" s="16"/>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <f t="shared" ref="A4:A7" si="0">A3+1</f>
         <v>3</v>
@@ -4191,7 +4200,7 @@
       <c r="D4" s="16"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4205,7 +4214,7 @@
       <c r="D5" s="16"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4221,7 +4230,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -4252,40 +4261,40 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7150B986-1239-4C03-963F-0D442EE47127}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.109375" style="1"/>
-    <col min="5" max="6" width="29.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="1"/>
-    <col min="8" max="8" width="64.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="1"/>
+    <col min="5" max="6" width="29.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="64.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.85546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" style="1" customWidth="1"/>
     <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="46.88671875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.109375" style="1"/>
-    <col min="18" max="18" width="41.88671875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="1"/>
+    <col min="14" max="14" width="18.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="46.85546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="41.85546875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="84" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-    </row>
-    <row r="2" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+    </row>
+    <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
@@ -4314,7 +4323,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>3</v>
       </c>
@@ -4337,43 +4346,43 @@
         <v>384</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="83" t="s">
+    <row r="4" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="84" t="s">
         <v>385</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-    </row>
-    <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="84" t="s">
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-    </row>
-    <row r="6" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+    </row>
+    <row r="6" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
@@ -4429,7 +4438,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A7" s="51">
         <v>1</v>
       </c>
@@ -4463,7 +4472,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2</v>
       </c>
@@ -4497,43 +4506,43 @@
         <v>390</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="83" t="s">
+    <row r="9" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="84" t="s">
         <v>391</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-    </row>
-    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="84" t="s">
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="84"/>
+    </row>
+    <row r="10" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84"/>
-      <c r="M10" s="84"/>
-      <c r="N10" s="84"/>
-    </row>
-    <row r="11" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+    </row>
+    <row r="11" spans="1:18" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
@@ -4581,7 +4590,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A12" s="51">
         <f>[1]Update!A12+1</f>
         <v>8</v>
@@ -4614,7 +4623,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="288" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="300" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="e">
         <f>#REF!+1</f>
         <v>#REF!</v>
@@ -4649,105 +4658,105 @@
         <v>390</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="83" t="s">
+    <row r="14" spans="1:18" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="84" t="s">
         <v>393</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
       <c r="O14" s="55"/>
     </row>
-    <row r="15" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="81" t="s">
+    <row r="15" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="82" t="s">
         <v>394</v>
       </c>
-      <c r="B15" s="81"/>
-      <c r="C15" s="81"/>
-    </row>
-    <row r="16" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="82" t="s">
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+    </row>
+    <row r="16" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="83" t="s">
         <v>395</v>
       </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-    </row>
-    <row r="17" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82" t="s">
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+    </row>
+    <row r="17" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="83" t="s">
         <v>396</v>
       </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82"/>
-    </row>
-    <row r="18" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="82" t="s">
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+    </row>
+    <row r="18" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="83" t="s">
         <v>397</v>
       </c>
-      <c r="B18" s="82"/>
-      <c r="C18" s="82"/>
-    </row>
-    <row r="19" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="82" t="s">
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+    </row>
+    <row r="19" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="83" t="s">
         <v>398</v>
       </c>
-      <c r="B19" s="82"/>
-      <c r="C19" s="82"/>
-    </row>
-    <row r="20" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="82" t="s">
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+    </row>
+    <row r="20" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="83" t="s">
         <v>399</v>
       </c>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-    </row>
-    <row r="21" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="82" t="s">
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+    </row>
+    <row r="21" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="83" t="s">
         <v>400</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-    </row>
-    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="83" t="s">
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+    </row>
+    <row r="22" spans="1:14" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A22" s="84" t="s">
         <v>401</v>
       </c>
-      <c r="B22" s="83"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="83"/>
-    </row>
-    <row r="23" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="81" t="s">
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+    </row>
+    <row r="23" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="82" t="s">
         <v>399</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
-    </row>
-    <row r="24" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="82" t="s">
+      <c r="B23" s="82"/>
+      <c r="C23" s="82"/>
+    </row>
+    <row r="24" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="83" t="s">
         <v>400</v>
       </c>
-      <c r="B24" s="82"/>
-      <c r="C24" s="82"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4776,161 +4785,161 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AA9480-FECE-4D77-AD12-36E3BA69C1AC}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:P260"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="4"/>
-    <col min="2" max="2" width="32.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="32.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="8" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" customWidth="1"/>
-    <col min="8" max="8" width="50.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" customWidth="1"/>
-    <col min="14" max="15" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="8" max="8" width="50.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="15" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:16" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="70" t="s">
         <v>402</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-    </row>
-    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="87" t="s">
         <v>403</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="88" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="89" t="s">
         <v>404</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
-      <c r="K5" s="89"/>
-      <c r="L5" s="89"/>
-      <c r="M5" s="89"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="72" t="s">
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-    </row>
-    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="85" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+    </row>
+    <row r="7" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="67"/>
-    </row>
-    <row r="8" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="68"/>
+    </row>
+    <row r="8" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>41</v>
       </c>
@@ -4980,7 +4989,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>1</v>
       </c>
@@ -5016,7 +5025,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <f>A9+1</f>
         <v>2</v>
@@ -5051,7 +5060,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f t="shared" ref="A11:A74" si="0">A10+1</f>
         <v>3</v>
@@ -5086,7 +5095,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5121,7 +5130,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -5156,7 +5165,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5191,7 +5200,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5226,7 +5235,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5261,7 +5270,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5296,7 +5305,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5331,7 +5340,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5368,7 +5377,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5403,7 +5412,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -5438,7 +5447,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -5473,7 +5482,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -5508,7 +5517,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -5543,7 +5552,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -5578,7 +5587,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -5613,7 +5622,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -5648,7 +5657,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -5683,7 +5692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5718,7 +5727,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -5753,7 +5762,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -5790,7 +5799,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -5827,7 +5836,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -5864,7 +5873,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -5901,7 +5910,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -5938,7 +5947,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -5975,7 +5984,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6012,7 +6021,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6049,7 +6058,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -6086,7 +6095,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6121,7 +6130,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -6158,7 +6167,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -6195,7 +6204,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -6232,7 +6241,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -6269,7 +6278,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -6306,7 +6315,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -6343,7 +6352,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="17">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -6380,7 +6389,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="17">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -6417,7 +6426,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="17">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -6452,7 +6461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="17">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -6489,7 +6498,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -6524,7 +6533,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="17">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -6561,7 +6570,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="17">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -6598,7 +6607,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="17">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -6635,7 +6644,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="17">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -6670,7 +6679,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="17">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -6705,7 +6714,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="17">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -6742,7 +6751,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="17">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -6779,7 +6788,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="17">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -6816,7 +6825,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="17">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -6853,7 +6862,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="17">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -6890,7 +6899,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="17">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -6927,7 +6936,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="17">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -6962,7 +6971,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="17">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -6997,7 +7006,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="17">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -7032,7 +7041,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="17">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -7067,7 +7076,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="17">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -7102,7 +7111,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="17">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -7137,7 +7146,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="17">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -7172,7 +7181,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="17">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -7207,7 +7216,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="17">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -7242,7 +7251,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="17">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -7277,7 +7286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="17">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -7312,7 +7321,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="17">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -7347,7 +7356,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="17">
         <f t="shared" ref="A75:A128" si="1">A74+1</f>
         <v>67</v>
@@ -7382,7 +7391,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="17">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -7417,7 +7426,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="17">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -7454,7 +7463,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="17">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -7489,7 +7498,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="17">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -7526,7 +7535,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="17">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -7563,7 +7572,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="17">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -7598,7 +7607,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="17">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -7635,7 +7644,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="17">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -7672,7 +7681,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="17">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -7709,7 +7718,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="17">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -7744,7 +7753,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="17">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -7779,7 +7788,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="17">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -7814,7 +7823,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="17">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -7849,7 +7858,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="17">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -7884,7 +7893,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="17">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -7919,7 +7928,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="17">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -7954,7 +7963,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="17">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -7989,7 +7998,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="17">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -8026,7 +8035,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="17">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -8063,7 +8072,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="17">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -8100,7 +8109,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="17">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -8135,7 +8144,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="17">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -8172,7 +8181,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="17">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -8209,7 +8218,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="17">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -8244,7 +8253,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="17">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -8279,7 +8288,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="17">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -8314,7 +8323,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="17">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -8351,7 +8360,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="17">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -8388,7 +8397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="17">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -8425,7 +8434,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="17">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -8458,7 +8467,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="17">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -8493,7 +8502,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="17">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -8528,7 +8537,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="17">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -8563,7 +8572,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="17">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -8598,7 +8607,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="17">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -8633,7 +8642,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="17">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -8668,7 +8677,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="17">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -8703,7 +8712,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="17">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -8738,7 +8747,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="17">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -8773,7 +8782,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="17">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -8808,7 +8817,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="17">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -8843,7 +8852,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="17">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -8880,7 +8889,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="17">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -8915,7 +8924,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="17">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -8950,7 +8959,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="17">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -8985,7 +8994,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="17">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -9020,7 +9029,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="17">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -9055,7 +9064,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="17">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -9090,7 +9099,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="17">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -9125,7 +9134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="17">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -9160,7 +9169,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="17">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -9195,7 +9204,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="17">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -9230,7 +9239,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="17">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -9265,26 +9274,26 @@
         <v>62</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="70" t="s">
+    <row r="129" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="71" t="s">
         <v>305</v>
       </c>
-      <c r="B129" s="70"/>
-      <c r="C129" s="70"/>
-      <c r="D129" s="70"/>
-      <c r="E129" s="70"/>
-      <c r="F129" s="70"/>
-      <c r="G129" s="70"/>
-      <c r="H129" s="70"/>
-      <c r="I129" s="70"/>
-      <c r="J129" s="70"/>
-      <c r="K129" s="70"/>
-      <c r="L129" s="70"/>
-      <c r="M129" s="70"/>
-      <c r="N129" s="70"/>
+      <c r="B129" s="71"/>
+      <c r="C129" s="71"/>
+      <c r="D129" s="71"/>
+      <c r="E129" s="71"/>
+      <c r="F129" s="71"/>
+      <c r="G129" s="71"/>
+      <c r="H129" s="71"/>
+      <c r="I129" s="71"/>
+      <c r="J129" s="71"/>
+      <c r="K129" s="71"/>
+      <c r="L129" s="71"/>
+      <c r="M129" s="71"/>
+      <c r="N129" s="71"/>
       <c r="O129" s="19"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
         <v>1</v>
       </c>
@@ -9310,7 +9319,7 @@
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
         <f>A130+1</f>
         <v>2</v>
@@ -9335,7 +9344,7 @@
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
         <f t="shared" ref="A132:A136" si="2">A131+1</f>
         <v>3</v>
@@ -9360,7 +9369,7 @@
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -9385,7 +9394,7 @@
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -9410,7 +9419,7 @@
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
     </row>
-    <row r="135" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -9439,7 +9448,7 @@
       </c>
       <c r="N135" s="2"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -9466,17 +9475,17 @@
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B141" s="8" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>60</v>
       </c>
@@ -9484,7 +9493,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>60</v>
       </c>
@@ -9492,7 +9501,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>60</v>
       </c>
@@ -9500,7 +9509,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>60</v>
       </c>
@@ -9508,7 +9517,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>60</v>
       </c>
@@ -9516,7 +9525,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>60</v>
       </c>
@@ -9524,7 +9533,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>60</v>
       </c>
@@ -9532,7 +9541,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>60</v>
       </c>
@@ -9540,7 +9549,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>60</v>
       </c>
@@ -9548,7 +9557,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>60</v>
       </c>
@@ -9556,7 +9565,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>60</v>
       </c>
@@ -9564,7 +9573,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>60</v>
       </c>
@@ -9572,7 +9581,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>60</v>
       </c>
@@ -9580,7 +9589,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>60</v>
       </c>
@@ -9588,7 +9597,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>60</v>
       </c>
@@ -9596,7 +9605,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>60</v>
       </c>
@@ -9604,7 +9613,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>60</v>
       </c>
@@ -9612,7 +9621,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>60</v>
       </c>
@@ -9620,7 +9629,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>60</v>
       </c>
@@ -9628,7 +9637,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>60</v>
       </c>
@@ -9636,7 +9645,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>60</v>
       </c>
@@ -9644,7 +9653,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>60</v>
       </c>
@@ -9652,7 +9661,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>60</v>
       </c>
@@ -9660,7 +9669,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>60</v>
       </c>
@@ -9668,7 +9677,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>60</v>
       </c>
@@ -9676,7 +9685,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>60</v>
       </c>
@@ -9684,7 +9693,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>60</v>
       </c>
@@ -9692,7 +9701,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>60</v>
       </c>
@@ -9700,7 +9709,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>60</v>
       </c>
@@ -9708,7 +9717,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>60</v>
       </c>
@@ -9716,7 +9725,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>60</v>
       </c>
@@ -9724,7 +9733,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>60</v>
       </c>
@@ -9732,7 +9741,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>60</v>
       </c>
@@ -9740,7 +9749,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>60</v>
       </c>
@@ -9748,7 +9757,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>60</v>
       </c>
@@ -9756,7 +9765,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>60</v>
       </c>
@@ -9764,7 +9773,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>60</v>
       </c>
@@ -9772,7 +9781,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>60</v>
       </c>
@@ -9780,7 +9789,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>60</v>
       </c>
@@ -9788,7 +9797,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>60</v>
       </c>
@@ -9796,7 +9805,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>60</v>
       </c>
@@ -9804,7 +9813,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>60</v>
       </c>
@@ -9812,7 +9821,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>60</v>
       </c>
@@ -9820,7 +9829,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>60</v>
       </c>
@@ -9828,7 +9837,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>60</v>
       </c>
@@ -9836,7 +9845,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>60</v>
       </c>
@@ -9844,7 +9853,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>60</v>
       </c>
@@ -9852,7 +9861,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>60</v>
       </c>
@@ -9860,7 +9869,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>60</v>
       </c>
@@ -9868,7 +9877,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>60</v>
       </c>
@@ -9876,7 +9885,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>60</v>
       </c>
@@ -9884,7 +9893,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>60</v>
       </c>
@@ -9892,7 +9901,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>60</v>
       </c>
@@ -9900,7 +9909,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>60</v>
       </c>
@@ -9908,7 +9917,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>60</v>
       </c>
@@ -9916,7 +9925,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>60</v>
       </c>
@@ -9924,7 +9933,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>60</v>
       </c>
@@ -9932,7 +9941,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>60</v>
       </c>
@@ -9940,7 +9949,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>60</v>
       </c>
@@ -9948,7 +9957,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>60</v>
       </c>
@@ -9956,7 +9965,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>60</v>
       </c>
@@ -9964,7 +9973,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>60</v>
       </c>
@@ -9972,7 +9981,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>60</v>
       </c>
@@ -9980,7 +9989,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>60</v>
       </c>
@@ -9988,7 +9997,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>60</v>
       </c>
@@ -9996,7 +10005,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>60</v>
       </c>
@@ -10004,7 +10013,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>60</v>
       </c>
@@ -10012,7 +10021,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>60</v>
       </c>
@@ -10020,7 +10029,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>60</v>
       </c>
@@ -10028,7 +10037,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>60</v>
       </c>
@@ -10036,7 +10045,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>60</v>
       </c>
@@ -10044,7 +10053,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>60</v>
       </c>
@@ -10052,7 +10061,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>60</v>
       </c>
@@ -10060,7 +10069,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>60</v>
       </c>
@@ -10068,7 +10077,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>60</v>
       </c>
@@ -10076,7 +10085,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>60</v>
       </c>
@@ -10084,7 +10093,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>60</v>
       </c>
@@ -10092,7 +10101,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>60</v>
       </c>
@@ -10100,7 +10109,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>60</v>
       </c>
@@ -10108,7 +10117,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>60</v>
       </c>
@@ -10116,7 +10125,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>60</v>
       </c>
@@ -10124,7 +10133,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>60</v>
       </c>
@@ -10132,7 +10141,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>60</v>
       </c>
@@ -10140,7 +10149,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>60</v>
       </c>
@@ -10148,7 +10157,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>60</v>
       </c>
@@ -10156,7 +10165,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>60</v>
       </c>
@@ -10164,7 +10173,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>60</v>
       </c>
@@ -10172,7 +10181,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>60</v>
       </c>
@@ -10180,7 +10189,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>60</v>
       </c>
@@ -10188,7 +10197,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>60</v>
       </c>
@@ -10196,7 +10205,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>60</v>
       </c>
@@ -10204,7 +10213,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>60</v>
       </c>
@@ -10212,7 +10221,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>60</v>
       </c>
@@ -10220,7 +10229,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>60</v>
       </c>
@@ -10228,7 +10237,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>60</v>
       </c>
@@ -10236,7 +10245,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>60</v>
       </c>
@@ -10244,7 +10253,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>60</v>
       </c>
@@ -10252,7 +10261,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>60</v>
       </c>
@@ -10260,7 +10269,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>60</v>
       </c>
@@ -10268,7 +10277,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>60</v>
       </c>
@@ -10276,7 +10285,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>60</v>
       </c>
@@ -10284,7 +10293,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>60</v>
       </c>
@@ -10292,7 +10301,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>60</v>
       </c>
@@ -10300,7 +10309,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>60</v>
       </c>
@@ -10308,7 +10317,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>60</v>
       </c>
@@ -10316,7 +10325,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>60</v>
       </c>
@@ -10324,7 +10333,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>60</v>
       </c>
@@ -10332,7 +10341,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>60</v>
       </c>
@@ -10340,7 +10349,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>60</v>
       </c>
@@ -10348,7 +10357,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>60</v>
       </c>
@@ -10356,7 +10365,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>60</v>
       </c>
@@ -10364,7 +10373,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>60</v>
       </c>
@@ -10372,7 +10381,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>60</v>
       </c>
@@ -10380,7 +10389,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>60</v>
       </c>
@@ -10388,7 +10397,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>60</v>
       </c>
@@ -10396,7 +10405,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>60</v>
       </c>
@@ -10404,7 +10413,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>60</v>
       </c>
@@ -10412,7 +10421,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>60</v>
       </c>
@@ -10420,7 +10429,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>60</v>
       </c>
@@ -10452,15 +10461,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD98F21-BD81-41C2-B163-E6FB5351BA37}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="82" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>20</v>
       </c>
@@ -10474,7 +10483,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="61">
         <v>1</v>
       </c>
@@ -10488,7 +10497,7 @@
         <v>45253</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>1.1000000000000001</v>
       </c>
@@ -10502,11 +10511,11 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="65">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="66">
         <v>1.2</v>
       </c>
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="66" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="59" t="s">
@@ -10516,9 +10525,9 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="66"/>
+      <c r="B5" s="66"/>
       <c r="C5" s="60" t="s">
         <v>29</v>
       </c>
@@ -10527,9 +10536,9 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
       <c r="C6" s="60" t="s">
         <v>30</v>
       </c>
@@ -10538,9 +10547,9 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="65"/>
-      <c r="B7" s="65"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="66"/>
+      <c r="B7" s="66"/>
       <c r="C7" s="26" t="s">
         <v>31</v>
       </c>
@@ -10549,7 +10558,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>1.3</v>
       </c>
@@ -10563,7 +10572,7 @@
         <v>45280</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>1.4</v>
       </c>
@@ -10577,7 +10586,7 @@
         <v>44934</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>1.5</v>
       </c>
@@ -10591,7 +10600,7 @@
         <v>44943</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>1.6</v>
       </c>
@@ -10605,7 +10614,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>1.7</v>
       </c>
@@ -10631,199 +10640,184 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4562C33-095E-4103-B008-03879D66799D}">
-  <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="50.5546875" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" customWidth="1"/>
-    <col min="9" max="9" width="61.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" customWidth="1"/>
-    <col min="13" max="13" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" customWidth="1"/>
+    <col min="9" max="9" width="61.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:17" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-    </row>
-    <row r="2" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+    </row>
+    <row r="2" spans="1:17" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>786</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>787</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+    </row>
+    <row r="3" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="72" t="s">
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-    </row>
-    <row r="4" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+    </row>
+    <row r="5" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-    </row>
-    <row r="5" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+    </row>
+    <row r="6" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P6" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q6" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="7" spans="1:17" ht="225" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>1</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -10840,26 +10834,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="17" cm="1">
         <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>62</v>
+        <v>23</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
@@ -10876,56 +10870,60 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="17" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="74"/>
-      <c r="I9" s="1" t="s">
-        <v>68</v>
+      <c r="H9" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="17" cm="1">
         <f t="array" aca="1" ref="A10" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="H10" s="75"/>
+      <c r="I10" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -10934,23 +10932,21 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="17" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>23</v>
@@ -10959,7 +10955,7 @@
         <v>62</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -10970,33 +10966,33 @@
       <c r="P11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q11" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="17" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -11006,29 +11002,31 @@
       </c>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="17" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -11038,26 +11036,26 @@
       </c>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="17" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -11070,17 +11068,17 @@
       </c>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:17" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="17" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" t="s">
-        <v>80</v>
+      <c r="F15" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>59</v>
@@ -11088,37 +11086,31 @@
       <c r="H15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>81</v>
+      <c r="I15" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="J15" s="2"/>
-      <c r="K15" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
-      <c r="M15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="225" x14ac:dyDescent="0.25">
       <c r="A16" s="17" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
-        <v>83</v>
+      <c r="F16" t="s">
+        <v>80</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>59</v>
@@ -11126,39 +11118,46 @@
       <c r="H16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>84</v>
+      <c r="I16" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="M16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="17" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -11170,53 +11169,48 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="17" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
-      <c r="N18" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="2"/>
-    </row>
-    <row r="19" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="17" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>59</v>
@@ -11225,7 +11219,7 @@
         <v>62</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>89</v>
@@ -11233,167 +11227,170 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="N19" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" s="1" customFormat="1" ht="216" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="17" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>14</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q20" s="2"/>
+    </row>
+    <row r="21" spans="1:17" s="1" customFormat="1" ht="285" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" cm="1">
+        <f t="array" aca="1" ref="A21" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>15</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="66" t="s">
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="68"/>
-    </row>
-    <row r="22" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="69"/>
+    </row>
+    <row r="23" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L23" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="M23" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="N23" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>1</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="17">
-        <f>A23+1</f>
-        <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E24" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>60</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -11401,20 +11398,20 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
-        <f t="shared" ref="A25:A26" si="0">A24+1</f>
-        <v>3</v>
+        <f>A24+1</f>
+        <v>2</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>59</v>
@@ -11423,23 +11420,21 @@
         <v>60</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
-      <c r="N25" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" ref="A26:A27" si="0">A25+1</f>
+        <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>98</v>
@@ -11449,10 +11444,10 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>60</v>
@@ -11461,7 +11456,7 @@
         <v>62</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -11471,23 +11466,58 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P27" xr:uid="{C4562C33-095E-4103-B008-03879D66799D}"/>
+  <autoFilter ref="A6:P28" xr:uid="{C4562C33-095E-4103-B008-03879D66799D}"/>
   <mergeCells count="6">
-    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A22:N22"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A5:N5"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H9:H10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A27" location="Index!A1" display="Back to Index" xr:uid="{507B2FF7-EFED-45E9-8DA9-54388F11BE20}"/>
+    <hyperlink ref="A28" location="Index!A1" display="Back to Index" xr:uid="{507B2FF7-EFED-45E9-8DA9-54388F11BE20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11497,14 +11527,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38C28DD-7D9E-4F69-A545-F0C75896CB2C}">
   <dimension ref="A2:Q92"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="74.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="e">
         <f>Create!#REF!+1</f>
         <v>#REF!</v>
@@ -11534,7 +11564,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="e">
         <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>#REF!</v>
@@ -11564,7 +11594,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11594,7 +11624,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11624,7 +11654,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11654,7 +11684,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11684,7 +11714,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11714,7 +11744,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11744,7 +11774,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11774,7 +11804,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="150" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11804,7 +11834,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11836,7 +11866,7 @@
       </c>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11868,7 +11898,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11900,7 +11930,7 @@
       </c>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11930,7 +11960,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11960,7 +11990,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="29"/>
     </row>
-    <row r="17" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -11992,7 +12022,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="29"/>
     </row>
-    <row r="18" spans="1:15" ht="39" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="39.75" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12022,7 +12052,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="29"/>
     </row>
-    <row r="19" spans="1:15" ht="147" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="159.75" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12052,7 +12082,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="29"/>
     </row>
-    <row r="20" spans="1:15" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="315" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12082,7 +12112,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="29"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12114,7 +12144,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="29"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12146,7 +12176,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="29"/>
     </row>
-    <row r="23" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12180,7 +12210,7 @@
       </c>
       <c r="O23" s="29"/>
     </row>
-    <row r="24" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12212,7 +12242,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="29"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12242,7 +12272,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="29"/>
     </row>
-    <row r="26" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12276,7 +12306,7 @@
       </c>
       <c r="O26" s="29"/>
     </row>
-    <row r="27" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12308,7 +12338,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="29"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12340,7 +12370,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="29"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12372,7 +12402,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="29"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12404,7 +12434,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="29"/>
     </row>
-    <row r="31" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12438,7 +12468,7 @@
       </c>
       <c r="O31" s="29"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12470,7 +12500,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="29"/>
     </row>
-    <row r="33" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12502,7 +12532,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="29"/>
     </row>
-    <row r="34" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
@@ -12536,7 +12566,7 @@
       </c>
       <c r="O34" s="29"/>
     </row>
-    <row r="35" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="e">
         <f t="shared" ref="A35:A66" si="1">A34+1</f>
         <v>#REF!</v>
@@ -12564,7 +12594,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="29"/>
     </row>
-    <row r="36" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12598,7 +12628,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="29"/>
     </row>
-    <row r="37" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12630,7 +12660,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="29"/>
     </row>
-    <row r="38" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12662,7 +12692,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="29"/>
     </row>
-    <row r="39" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12696,7 +12726,7 @@
       </c>
       <c r="O39" s="29"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12728,7 +12758,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="29"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12758,7 +12788,7 @@
       <c r="N41" s="2"/>
       <c r="O41" s="29"/>
     </row>
-    <row r="42" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12790,7 +12820,7 @@
       <c r="N42" s="2"/>
       <c r="O42" s="29"/>
     </row>
-    <row r="43" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12824,7 +12854,7 @@
       </c>
       <c r="O43" s="29"/>
     </row>
-    <row r="44" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12856,7 +12886,7 @@
       <c r="N44" s="2"/>
       <c r="O44" s="29"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12888,7 +12918,7 @@
       <c r="N45" s="2"/>
       <c r="O45" s="29"/>
     </row>
-    <row r="46" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12922,7 +12952,7 @@
       </c>
       <c r="O46" s="29"/>
     </row>
-    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12954,7 +12984,7 @@
       <c r="N47" s="2"/>
       <c r="O47" s="29"/>
     </row>
-    <row r="48" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -12986,7 +13016,7 @@
       <c r="N48" s="2"/>
       <c r="O48" s="29"/>
     </row>
-    <row r="49" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13020,7 +13050,7 @@
       </c>
       <c r="O49" s="29"/>
     </row>
-    <row r="50" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13052,7 +13082,7 @@
       <c r="N50" s="2"/>
       <c r="O50" s="29"/>
     </row>
-    <row r="51" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13084,7 +13114,7 @@
       <c r="N51" s="2"/>
       <c r="O51" s="29"/>
     </row>
-    <row r="52" spans="1:15" ht="216" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="240" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13116,7 +13146,7 @@
       <c r="N52" s="2"/>
       <c r="O52" s="29"/>
     </row>
-    <row r="53" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13150,7 +13180,7 @@
       </c>
       <c r="O53" s="29"/>
     </row>
-    <row r="54" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13182,7 +13212,7 @@
       <c r="N54" s="2"/>
       <c r="O54" s="29"/>
     </row>
-    <row r="55" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13214,7 +13244,7 @@
       <c r="N55" s="2"/>
       <c r="O55" s="29"/>
     </row>
-    <row r="56" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13248,7 +13278,7 @@
       </c>
       <c r="O56" s="29"/>
     </row>
-    <row r="57" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13280,7 +13310,7 @@
       <c r="N57" s="2"/>
       <c r="O57" s="29"/>
     </row>
-    <row r="58" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13312,7 +13342,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="29"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13344,7 +13374,7 @@
       <c r="N59" s="2"/>
       <c r="O59" s="29"/>
     </row>
-    <row r="60" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13376,7 +13406,7 @@
       <c r="N60" s="2"/>
       <c r="O60" s="29"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13408,7 +13438,7 @@
       <c r="N61" s="2"/>
       <c r="O61" s="29"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13438,7 +13468,7 @@
       <c r="N62" s="2"/>
       <c r="O62" s="29"/>
     </row>
-    <row r="63" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13470,7 +13500,7 @@
       <c r="N63" s="2"/>
       <c r="O63" s="29"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13500,7 +13530,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="29"/>
     </row>
-    <row r="65" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13530,7 +13560,7 @@
       <c r="N65" s="2"/>
       <c r="O65" s="29"/>
     </row>
-    <row r="66" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -13562,7 +13592,7 @@
       </c>
       <c r="O66" s="29"/>
     </row>
-    <row r="67" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="e">
         <f t="shared" ref="A67:A92" si="2">A66+1</f>
         <v>#REF!</v>
@@ -13592,7 +13622,7 @@
       <c r="N67" s="2"/>
       <c r="O67" s="29"/>
     </row>
-    <row r="68" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13622,7 +13652,7 @@
       <c r="N68" s="2"/>
       <c r="O68" s="29"/>
     </row>
-    <row r="69" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13652,7 +13682,7 @@
       <c r="N69" s="2"/>
       <c r="O69" s="29"/>
     </row>
-    <row r="70" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13684,7 +13714,7 @@
       </c>
       <c r="O70" s="29"/>
     </row>
-    <row r="71" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13714,7 +13744,7 @@
       <c r="N71" s="2"/>
       <c r="O71" s="29"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13744,7 +13774,7 @@
       <c r="N72" s="2"/>
       <c r="O72" s="29"/>
     </row>
-    <row r="73" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13774,7 +13804,7 @@
       <c r="N73" s="2"/>
       <c r="O73" s="29"/>
     </row>
-    <row r="74" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13804,7 +13834,7 @@
       <c r="N74" s="2"/>
       <c r="O74" s="29"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13834,7 +13864,7 @@
       <c r="N75" s="2"/>
       <c r="O75" s="29"/>
     </row>
-    <row r="76" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13866,7 +13896,7 @@
       </c>
       <c r="O76" s="29"/>
     </row>
-    <row r="77" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13896,7 +13926,7 @@
       <c r="N77" s="2"/>
       <c r="O77" s="29"/>
     </row>
-    <row r="78" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="240" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13926,7 +13956,7 @@
       <c r="N78" s="2"/>
       <c r="O78" s="29"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13956,7 +13986,7 @@
       <c r="N79" s="2"/>
       <c r="O79" s="29"/>
     </row>
-    <row r="80" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -13986,7 +14016,7 @@
       <c r="N80" s="2"/>
       <c r="O80" s="29"/>
     </row>
-    <row r="81" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14016,7 +14046,7 @@
       <c r="N81" s="2"/>
       <c r="O81" s="29"/>
     </row>
-    <row r="82" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14048,7 +14078,7 @@
       <c r="N82" s="2"/>
       <c r="O82" s="29"/>
     </row>
-    <row r="83" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14078,7 +14108,7 @@
       <c r="N83" s="2"/>
       <c r="O83" s="29"/>
     </row>
-    <row r="84" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14108,7 +14138,7 @@
       <c r="N84" s="2"/>
       <c r="O84" s="29"/>
     </row>
-    <row r="85" spans="1:17" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" ht="210" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14140,7 +14170,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="29"/>
     </row>
-    <row r="86" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14170,7 +14200,7 @@
       <c r="N86" s="2"/>
       <c r="O86" s="29"/>
     </row>
-    <row r="87" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14200,7 +14230,7 @@
       <c r="N87" s="2"/>
       <c r="O87" s="29"/>
     </row>
-    <row r="88" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14231,7 +14261,7 @@
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
     </row>
-    <row r="89" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14262,7 +14292,7 @@
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
     </row>
-    <row r="90" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14293,7 +14323,7 @@
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
     </row>
-    <row r="91" spans="1:17" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14323,11 +14353,11 @@
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
-      <c r="Q91" s="75" t="s">
+      <c r="Q91" s="76" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -14357,7 +14387,7 @@
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
-      <c r="Q92" s="75"/>
+      <c r="Q92" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14370,187 +14400,173 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B5E853-2798-4156-AAAB-0750264D3328}">
-  <dimension ref="A1:P28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="8" max="8" width="65.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="65.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-    </row>
-    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+    </row>
+    <row r="2" spans="1:16" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>786</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>787</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+    </row>
+    <row r="3" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="72" t="s">
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-    </row>
-    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="70" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+    </row>
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-    </row>
-    <row r="5" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+    </row>
+    <row r="6" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="7" spans="1:16" ht="225" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>1</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I7" s="42" t="s">
         <v>60</v>
@@ -14566,31 +14582,33 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="17" cm="1">
         <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I8" s="42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -14598,59 +14616,57 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="17" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="180" x14ac:dyDescent="0.25">
       <c r="A10" s="17" cm="1">
         <f t="array" aca="1" ref="A10" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>96</v>
+        <v>291</v>
       </c>
       <c r="I10" s="42" t="s">
         <v>60</v>
@@ -14659,59 +14675,56 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="O10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:16" ht="255" x14ac:dyDescent="0.25">
       <c r="A11" s="17" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="I11" s="41" t="s">
-        <v>62</v>
+        <v>96</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>60</v>
       </c>
       <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="17" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>59</v>
@@ -14720,7 +14733,7 @@
         <v>62</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I12" s="41" t="s">
         <v>62</v>
@@ -14733,105 +14746,107 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P12" s="43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="17" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>70</v>
+        <v>293</v>
       </c>
       <c r="I13" s="41" t="s">
         <v>62</v>
       </c>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" cm="1">
-        <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>1</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="O13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P13" s="43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" cm="1">
+        <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>8</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="17" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I16" s="41" t="s">
         <v>62</v>
       </c>
       <c r="J16" s="2"/>
-      <c r="K16" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -14840,31 +14855,33 @@
       </c>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="17" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I17" s="41" t="s">
         <v>62</v>
       </c>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -14873,25 +14890,25 @@
       </c>
       <c r="P17" s="2"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="17" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I18" s="41" t="s">
         <v>62</v>
@@ -14906,16 +14923,16 @@
       </c>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="17" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>59</v>
@@ -14924,35 +14941,31 @@
         <v>62</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="I19" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
         <v>60</v>
       </c>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="17" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>59</v>
@@ -14961,7 +14974,7 @@
         <v>62</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I20" s="41" t="s">
         <v>62</v>
@@ -14972,160 +14985,162 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
+      <c r="N20" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="O20" s="2" t="s">
         <v>60</v>
       </c>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="17" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
+        <v>6</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" cm="1">
+        <f t="array" aca="1" ref="A22" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>7</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="48" t="s">
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F22" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" s="57" t="s">
+      <c r="G22" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="57" t="s">
         <v>296</v>
       </c>
-      <c r="I21" s="41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="66" t="s">
+      <c r="I22" s="41" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A23" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="78"/>
-    </row>
-    <row r="23" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="79"/>
+    </row>
+    <row r="24" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I24" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J24" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K24" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L24" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="M24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="N24" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="17">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
         <v>1</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="17">
-        <f>A24+1</f>
-        <v>2</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D25" s="22" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G25" s="12" t="s">
         <v>60</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -15133,22 +15148,22 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
-        <f t="shared" ref="A26:A27" si="0">A25+1</f>
-        <v>3</v>
+        <f>A25+1</f>
+        <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D26" s="22" t="s">
         <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>59</v>
@@ -15157,23 +15172,21 @@
         <v>60</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="I26" s="20" t="s">
-        <v>62</v>
+        <v>102</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
-      <c r="N26" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" ref="A27:A28" si="0">A26+1</f>
+        <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>98</v>
@@ -15185,16 +15198,16 @@
         <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>60</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>107</v>
+        <v>297</v>
       </c>
       <c r="I27" s="20" t="s">
         <v>62</v>
@@ -15207,22 +15220,59 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P28" xr:uid="{66B5E853-2798-4156-AAAB-0750264D3328}"/>
+  <autoFilter ref="A6:P29" xr:uid="{66B5E853-2798-4156-AAAB-0750264D3328}"/>
   <mergeCells count="5">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A23:N23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A28" location="Index!A1" display="Back to Index" xr:uid="{CCAE1ABC-0F17-4336-B0AA-0AE835154C43}"/>
+    <hyperlink ref="A29" location="Index!A1" display="Back to Index" xr:uid="{CCAE1ABC-0F17-4336-B0AA-0AE835154C43}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15232,105 +15282,105 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5684969F-AACD-45AF-A496-A79457D4E01D}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:14" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="70" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+    </row>
+    <row r="2" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="72" t="s">
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="76" t="s">
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="77" t="s">
         <v>299</v>
       </c>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-    </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="70" t="s">
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+    </row>
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-    </row>
-    <row r="6" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+    </row>
+    <row r="6" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
@@ -15374,7 +15424,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -15404,25 +15454,25 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="66" t="s">
+    <row r="8" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="78"/>
-    </row>
-    <row r="9" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="78"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="79"/>
+    </row>
+    <row r="9" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>41</v>
       </c>
@@ -15466,7 +15516,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>1</v>
       </c>
@@ -15500,7 +15550,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f>A10+1</f>
         <v>2</v>
@@ -15533,7 +15583,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f>A11+1</f>
         <v>3</v>
@@ -15566,7 +15616,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>108</v>
       </c>
@@ -15589,358 +15639,345 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B4A248-C735-4C63-971A-A3F0609388EA}">
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.109375" style="8"/>
-    <col min="5" max="5" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="55.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="8"/>
+    <col min="5" max="5" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="55.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:14" s="4" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="80" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+    </row>
+    <row r="2" spans="1:14" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>786</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>787</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+    </row>
+    <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="72" t="s">
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="72" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="73" t="s">
         <v>302</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="72" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="73" t="s">
         <v>303</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="72" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="73" t="s">
         <v>304</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="72" t="s">
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-    </row>
-    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="70" t="s">
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+    </row>
+    <row r="9" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
-    </row>
-    <row r="9" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+    </row>
+    <row r="10" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="G11" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="70" t="s">
+      <c r="I11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="71" t="s">
         <v>305</v>
       </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="70"/>
-      <c r="N11" s="70"/>
-    </row>
-    <row r="12" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+    </row>
+    <row r="13" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <v>1</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <f>A13+1</f>
-        <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="22"/>
+        <v>62</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>60</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>60</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -15948,58 +15985,91 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f>A14+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="I15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <f>A15+1</f>
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A6:N6"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A12:N12"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A6:N6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A16" location="Index!A1" display="Back to Index" xr:uid="{2F7D9EE4-2416-40C7-AB98-A784D7AA5B56}"/>
+    <hyperlink ref="A17" location="Index!A1" display="Back to Index" xr:uid="{2F7D9EE4-2416-40C7-AB98-A784D7AA5B56}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16009,53 +16079,53 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4851DCD-305D-4BC9-A3EE-700C77EE9B14}">
   <dimension ref="A1:N43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="39.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="8" max="8" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
+    <row r="1" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="71" t="s">
         <v>307</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+    </row>
+    <row r="2" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-    </row>
-    <row r="3" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+    </row>
+    <row r="3" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
@@ -16099,7 +16169,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -16125,7 +16195,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="20"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="16" cm="1">
         <f t="array" aca="1" ref="A5" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>2</v>
@@ -16152,7 +16222,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="20"/>
     </row>
-    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="16" cm="1">
         <f t="array" aca="1" ref="A6" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>3</v>
@@ -16185,7 +16255,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" cm="1">
         <f t="array" aca="1" ref="A7" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>4</v>
@@ -16216,7 +16286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="16" cm="1">
         <f t="array" aca="1" ref="A8" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>5</v>
@@ -16235,7 +16305,7 @@
       <c r="G8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="80" t="s">
+      <c r="H8" s="81" t="s">
         <v>316</v>
       </c>
       <c r="I8" s="20" t="s">
@@ -16249,7 +16319,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="16" cm="1">
         <f t="array" aca="1" ref="A9" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>6</v>
@@ -16268,7 +16338,7 @@
       <c r="G9" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="80"/>
+      <c r="H9" s="81"/>
       <c r="I9" s="20" t="s">
         <v>60</v>
       </c>
@@ -16280,7 +16350,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="16" cm="1">
         <f t="array" aca="1" ref="A10" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>7</v>
@@ -16313,7 +16383,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="16" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>8</v>
@@ -16350,7 +16420,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="16" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>9</v>
@@ -16369,7 +16439,7 @@
       <c r="G12" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="80" t="s">
+      <c r="H12" s="81" t="s">
         <v>326</v>
       </c>
       <c r="I12" s="20" t="s">
@@ -16383,7 +16453,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="16" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>10</v>
@@ -16402,7 +16472,7 @@
       <c r="G13" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="80"/>
+      <c r="H13" s="81"/>
       <c r="I13" s="20" t="s">
         <v>60</v>
       </c>
@@ -16414,7 +16484,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="16" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>11</v>
@@ -16433,7 +16503,7 @@
       <c r="G14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="80" t="s">
+      <c r="H14" s="81" t="s">
         <v>329</v>
       </c>
       <c r="I14" s="20" t="s">
@@ -16447,7 +16517,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="16" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>12</v>
@@ -16466,7 +16536,7 @@
       <c r="G15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="80"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="20" t="s">
         <v>60</v>
       </c>
@@ -16478,7 +16548,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="16" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>13</v>
@@ -16497,7 +16567,7 @@
       <c r="G16" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="80" t="s">
+      <c r="H16" s="81" t="s">
         <v>332</v>
       </c>
       <c r="I16" s="20" t="s">
@@ -16511,7 +16581,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="16" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>14</v>
@@ -16530,7 +16600,7 @@
       <c r="G17" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="80"/>
+      <c r="H17" s="81"/>
       <c r="I17" s="20" t="s">
         <v>60</v>
       </c>
@@ -16542,7 +16612,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="16" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>15</v>
@@ -16575,7 +16645,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="16" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>16</v>
@@ -16612,7 +16682,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="16" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))+1</f>
         <v>17</v>
@@ -16643,7 +16713,7 @@
       <c r="M20" s="2"/>
       <c r="N20" s="20"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <f t="shared" ref="A21" ca="1" si="0">A20+1</f>
         <v>18</v>
@@ -16668,43 +16738,43 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="72" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="73" t="s">
         <v>339</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-    </row>
-    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A23" s="66" t="s">
+      <c r="B22" s="73"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+    </row>
+    <row r="23" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A23" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="77"/>
-      <c r="N23" s="78"/>
-    </row>
-    <row r="24" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="79"/>
+    </row>
+    <row r="24" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
@@ -16740,7 +16810,7 @@
       <c r="M24" s="25"/>
       <c r="N24" s="25"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>1</v>
       </c>
@@ -16759,7 +16829,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <f>A25+1</f>
         <v>2</v>
@@ -16782,7 +16852,7 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <f t="shared" ref="A27:A43" si="1">A26+1</f>
         <v>3</v>
@@ -16805,7 +16875,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -16828,7 +16898,7 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -16857,7 +16927,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -16888,7 +16958,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -16917,7 +16987,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -16946,7 +17016,7 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -16973,7 +17043,7 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -17002,7 +17072,7 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -17033,7 +17103,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -17062,7 +17132,7 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -17089,7 +17159,7 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -17116,7 +17186,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -17145,7 +17215,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -17172,7 +17242,7 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -17199,7 +17269,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -17226,7 +17296,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -17272,215 +17342,206 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29C083E-476D-4A78-BA90-146F808CAD00}">
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="69.5546875" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
+    <row r="1" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="71" t="s">
         <v>361</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+    </row>
+    <row r="2" spans="1:14" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>786</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>787</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+    </row>
+    <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-    </row>
-    <row r="3" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+    </row>
+    <row r="4" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="17">
+    <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="34" t="s">
+      <c r="G5" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="66" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="78"/>
-    </row>
-    <row r="6" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="78"/>
+      <c r="M6" s="78"/>
+      <c r="N6" s="79"/>
+    </row>
+    <row r="7" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="17">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
-        <f>A7+1</f>
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>59</v>
@@ -17488,16 +17549,16 @@
       <c r="G8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H8" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
-        <f t="shared" ref="A9:A22" si="0">A8+1</f>
-        <v>3</v>
+        <f>A8+1</f>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>363</v>
@@ -17509,434 +17570,463 @@
         <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>365</v>
+      <c r="G9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
+        <f t="shared" ref="A10:A23" si="0">A9+1</f>
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="C11" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="G11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C12" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="G12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="C13" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="G13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C13" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="C14" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="G14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C14" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="C15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="G15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="17">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="C16" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
         <v>73</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>59</v>
       </c>
-      <c r="G15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="G16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="22"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="I16" s="2"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="C17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="G17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="22"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="17">
+      <c r="I17" s="2"/>
+      <c r="J17" s="22"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C17" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="C18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="G18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="17">
+      <c r="I18" s="2"/>
+      <c r="J18" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C18" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="C19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="G19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="22"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="17">
+      <c r="I19" s="2"/>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C19" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="C20" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="G20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="17">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C20" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C21" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="38" t="s">
+      <c r="G21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="38" t="s">
         <v>374</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="17">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C21" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="C22" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="38" t="s">
+      <c r="G22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="38" t="s">
         <v>376</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="46">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="46">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C22" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="48" t="s">
+      <c r="C23" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F23" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" s="47" t="s">
+      <c r="G23" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="47" t="s">
         <v>377</v>
       </c>
-      <c r="I22" s="47"/>
-    </row>
-    <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
-        <f>A21+1</f>
+      <c r="I23" s="47"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <f>A22+1</f>
         <v>16</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B24" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="C24" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="G24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="I23" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="3"/>
+      <c r="I24" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J24" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A6:N6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17944,6 +18034,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009FF49975E8DE8E439848F855486C4ED8" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f39b8ea50b4efafd019d975ed3685cf0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4351ea0b-59b6-4bb2-9550-55596f432c66" xmlns:ns3="abb7c066-0e75-4f9f-a7fd-256dceefbfe6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6a7f805c69beeed54a184edbcd84b07f" ns2:_="" ns3:_="">
     <xsd:import namespace="4351ea0b-59b6-4bb2-9550-55596f432c66"/>
@@ -18120,12 +18216,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -18136,14 +18226,29 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E84BF0-81B0-4DF5-AD9D-9D6DEE0230FF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{632DF58F-9925-4F24-8594-A7A2396951DC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E84BF0-81B0-4DF5-AD9D-9D6DEE0230FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4351ea0b-59b6-4bb2-9550-55596f432c66"/>
+    <ds:schemaRef ds:uri="abb7c066-0e75-4f9f-a7fd-256dceefbfe6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
